--- a/data.mn/public/datasets/industrial-output-by-subdivision-monthly-mn.xlsx
+++ b/data.mn/public/datasets/industrial-output-by-subdivision-monthly-mn.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,64 +415,78 @@
   </sheetPr>
   <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>салбар</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -522,10 +524,10 @@
         <v>544.6</v>
       </c>
       <c r="K2" t="n">
-        <v>527.9</v>
+        <v>543.3</v>
       </c>
       <c r="L2" t="n">
-        <v>554.4</v>
+        <v>557.3</v>
       </c>
     </row>
     <row r="3">
@@ -560,10 +562,10 @@
         <v>391.3</v>
       </c>
       <c r="K3" t="n">
-        <v>539.5</v>
+        <v>553</v>
       </c>
       <c r="L3" t="n">
-        <v>481.5</v>
+        <v>483.2</v>
       </c>
     </row>
     <row r="4">
@@ -598,10 +600,10 @@
         <v>477.6</v>
       </c>
       <c r="K4" t="n">
-        <v>443.1</v>
+        <v>457</v>
       </c>
       <c r="L4" t="n">
-        <v>551.7</v>
+        <v>557.9</v>
       </c>
     </row>
     <row r="5">
@@ -636,9 +638,11 @@
         <v>513.5</v>
       </c>
       <c r="K5" t="n">
-        <v>519.1</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+        <v>532.9</v>
+      </c>
+      <c r="L5" t="n">
+        <v>664.4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -672,9 +676,11 @@
         <v>699.8</v>
       </c>
       <c r="K6" t="n">
-        <v>664.2</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
+        <v>674</v>
+      </c>
+      <c r="L6" t="n">
+        <v>814.1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -708,9 +714,11 @@
         <v>741.2</v>
       </c>
       <c r="K7" t="n">
-        <v>750.2</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
+        <v>755.4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1014.9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -744,9 +752,11 @@
         <v>664.1</v>
       </c>
       <c r="K8" t="n">
-        <v>623</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
+        <v>638.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>809.4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -780,7 +790,7 @@
         <v>674</v>
       </c>
       <c r="K9" t="n">
-        <v>888.8</v>
+        <v>896.6</v>
       </c>
       <c r="L9" t="inlineStr"/>
     </row>
@@ -818,7 +828,7 @@
         <v>664.5</v>
       </c>
       <c r="K10" t="n">
-        <v>907.6</v>
+        <v>927.1</v>
       </c>
       <c r="L10" t="inlineStr"/>
     </row>
@@ -856,7 +866,7 @@
         <v>650</v>
       </c>
       <c r="K11" t="n">
-        <v>828.3</v>
+        <v>849</v>
       </c>
       <c r="L11" t="inlineStr"/>
     </row>
@@ -894,7 +904,7 @@
         <v>618.6</v>
       </c>
       <c r="K12" t="n">
-        <v>687.7</v>
+        <v>703.8</v>
       </c>
       <c r="L12" t="inlineStr"/>
     </row>
@@ -932,7 +942,7 @@
         <v>627.3</v>
       </c>
       <c r="K13" t="n">
-        <v>748.9</v>
+        <v>760.8</v>
       </c>
       <c r="L13" t="inlineStr"/>
     </row>
@@ -971,7 +981,7 @@
         <v>26.2</v>
       </c>
       <c r="L14" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="15">
@@ -1009,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="L15" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="16">
@@ -1047,7 +1057,7 @@
         <v>25.3</v>
       </c>
       <c r="L16" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="17">
@@ -1084,7 +1094,9 @@
       <c r="K17" t="n">
         <v>25.6</v>
       </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>26.7</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1120,7 +1132,9 @@
       <c r="K18" t="n">
         <v>26.3</v>
       </c>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>26.7</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1156,7 +1170,9 @@
       <c r="K19" t="n">
         <v>24.2</v>
       </c>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>28.1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1192,7 +1208,9 @@
       <c r="K20" t="n">
         <v>22.4</v>
       </c>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>28.4</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1402,22 +1420,22 @@
         <v>796.2</v>
       </c>
       <c r="G26" t="n">
-        <v>920.4</v>
+        <v>945.3</v>
       </c>
       <c r="H26" t="n">
-        <v>1116.6</v>
+        <v>1120.7</v>
       </c>
       <c r="I26" t="n">
-        <v>2280.6</v>
+        <v>2304.7</v>
       </c>
       <c r="J26" t="n">
-        <v>2863.2</v>
+        <v>2878.5</v>
       </c>
       <c r="K26" t="n">
-        <v>2616.6</v>
+        <v>2651.9</v>
       </c>
       <c r="L26" t="n">
-        <v>4167.1</v>
+        <v>4224.5</v>
       </c>
     </row>
     <row r="27">
@@ -1440,22 +1458,22 @@
         <v>684.9</v>
       </c>
       <c r="G27" t="n">
-        <v>880.5</v>
+        <v>899.2</v>
       </c>
       <c r="H27" t="n">
-        <v>895.1</v>
+        <v>900.3</v>
       </c>
       <c r="I27" t="n">
-        <v>2053.6</v>
+        <v>2073.2</v>
       </c>
       <c r="J27" t="n">
-        <v>3059.7</v>
+        <v>3056.5</v>
       </c>
       <c r="K27" t="n">
-        <v>2453.6</v>
+        <v>2461.3</v>
       </c>
       <c r="L27" t="n">
-        <v>4373.5</v>
+        <v>4431.2</v>
       </c>
     </row>
     <row r="28">
@@ -1478,22 +1496,22 @@
         <v>697.8</v>
       </c>
       <c r="G28" t="n">
-        <v>1081.6</v>
+        <v>1106.1</v>
       </c>
       <c r="H28" t="n">
-        <v>973.5</v>
+        <v>981</v>
       </c>
       <c r="I28" t="n">
-        <v>2451</v>
+        <v>2471.9</v>
       </c>
       <c r="J28" t="n">
-        <v>3627.5</v>
+        <v>3622.6</v>
       </c>
       <c r="K28" t="n">
-        <v>2727.6</v>
+        <v>2744.8</v>
       </c>
       <c r="L28" t="n">
-        <v>5042.8</v>
+        <v>4997.2</v>
       </c>
     </row>
     <row r="29">
@@ -1516,21 +1534,23 @@
         <v>621.1</v>
       </c>
       <c r="G29" t="n">
-        <v>1013.8</v>
+        <v>1035.4</v>
       </c>
       <c r="H29" t="n">
-        <v>1196.9</v>
+        <v>1209.3</v>
       </c>
       <c r="I29" t="n">
-        <v>2433.9</v>
+        <v>2457.3</v>
       </c>
       <c r="J29" t="n">
-        <v>3685.6</v>
+        <v>3693.5</v>
       </c>
       <c r="K29" t="n">
-        <v>3246.3</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
+        <v>3249.5</v>
+      </c>
+      <c r="L29" t="n">
+        <v>4641.1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1552,21 +1572,23 @@
         <v>837.8</v>
       </c>
       <c r="G30" t="n">
-        <v>1121.5</v>
+        <v>1136.3</v>
       </c>
       <c r="H30" t="n">
-        <v>1197.3</v>
+        <v>1224.1</v>
       </c>
       <c r="I30" t="n">
-        <v>2304</v>
+        <v>2329.5</v>
       </c>
       <c r="J30" t="n">
-        <v>3924.2</v>
+        <v>3944.4</v>
       </c>
       <c r="K30" t="n">
-        <v>3564.3</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
+        <v>3575</v>
+      </c>
+      <c r="L30" t="n">
+        <v>5562.2</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1588,21 +1610,23 @@
         <v>1012</v>
       </c>
       <c r="G31" t="n">
-        <v>1057.4</v>
+        <v>1082.1</v>
       </c>
       <c r="H31" t="n">
-        <v>1360.6</v>
+        <v>1388.4</v>
       </c>
       <c r="I31" t="n">
-        <v>2281</v>
+        <v>2325.7</v>
       </c>
       <c r="J31" t="n">
-        <v>3804.8</v>
+        <v>3815.6</v>
       </c>
       <c r="K31" t="n">
-        <v>2916.7</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
+        <v>2924</v>
+      </c>
+      <c r="L31" t="n">
+        <v>5760.1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1624,21 +1648,23 @@
         <v>1043.8</v>
       </c>
       <c r="G32" t="n">
-        <v>1022.6</v>
+        <v>1045.3</v>
       </c>
       <c r="H32" t="n">
-        <v>1384.8</v>
+        <v>1397.7</v>
       </c>
       <c r="I32" t="n">
-        <v>2217.6</v>
+        <v>2251.5</v>
       </c>
       <c r="J32" t="n">
-        <v>3292.8</v>
+        <v>3303.8</v>
       </c>
       <c r="K32" t="n">
-        <v>3559.9</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
+        <v>3559.1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>5967.6</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1660,19 +1686,19 @@
         <v>1020.2</v>
       </c>
       <c r="G33" t="n">
-        <v>1037.2</v>
+        <v>1060.6</v>
       </c>
       <c r="H33" t="n">
-        <v>1972.3</v>
+        <v>1979.1</v>
       </c>
       <c r="I33" t="n">
-        <v>2916.5</v>
+        <v>2952.7</v>
       </c>
       <c r="J33" t="n">
-        <v>3257.3</v>
+        <v>3268</v>
       </c>
       <c r="K33" t="n">
-        <v>3772.4</v>
+        <v>3791.7</v>
       </c>
       <c r="L33" t="inlineStr"/>
     </row>
@@ -1698,19 +1724,19 @@
         <v>1285.5</v>
       </c>
       <c r="G34" t="n">
-        <v>1020.1</v>
+        <v>1033.6</v>
       </c>
       <c r="H34" t="n">
-        <v>2008.5</v>
+        <v>2026.4</v>
       </c>
       <c r="I34" t="n">
-        <v>2941.4</v>
+        <v>2979.3</v>
       </c>
       <c r="J34" t="n">
-        <v>3336.3</v>
+        <v>3353.2</v>
       </c>
       <c r="K34" t="n">
-        <v>3846</v>
+        <v>3850.4</v>
       </c>
       <c r="L34" t="inlineStr"/>
     </row>
@@ -1736,19 +1762,19 @@
         <v>1479.7</v>
       </c>
       <c r="G35" t="n">
-        <v>1137.5</v>
+        <v>1150.5</v>
       </c>
       <c r="H35" t="n">
-        <v>2158.1</v>
+        <v>2175.3</v>
       </c>
       <c r="I35" t="n">
-        <v>2814.7</v>
+        <v>2857.9</v>
       </c>
       <c r="J35" t="n">
-        <v>3682.4</v>
+        <v>3702.1</v>
       </c>
       <c r="K35" t="n">
-        <v>4187.7</v>
+        <v>4206.2</v>
       </c>
       <c r="L35" t="inlineStr"/>
     </row>
@@ -1774,19 +1800,19 @@
         <v>1363.5</v>
       </c>
       <c r="G36" t="n">
-        <v>995.5</v>
+        <v>1005.9</v>
       </c>
       <c r="H36" t="n">
-        <v>2044.5</v>
+        <v>2059.7</v>
       </c>
       <c r="I36" t="n">
-        <v>2938.1</v>
+        <v>2990.2</v>
       </c>
       <c r="J36" t="n">
-        <v>3222.9</v>
+        <v>3239</v>
       </c>
       <c r="K36" t="n">
-        <v>4247.6</v>
+        <v>4284.3</v>
       </c>
       <c r="L36" t="inlineStr"/>
     </row>
@@ -1812,19 +1838,19 @@
         <v>1390.6</v>
       </c>
       <c r="G37" t="n">
-        <v>899.1</v>
+        <v>901</v>
       </c>
       <c r="H37" t="n">
-        <v>2058.4</v>
+        <v>2075.7</v>
       </c>
       <c r="I37" t="n">
-        <v>2873.2</v>
+        <v>2912.3</v>
       </c>
       <c r="J37" t="n">
-        <v>3169.9</v>
+        <v>3191.4</v>
       </c>
       <c r="K37" t="n">
-        <v>4695.5</v>
+        <v>4774.1</v>
       </c>
       <c r="L37" t="inlineStr"/>
     </row>
@@ -1848,22 +1874,22 @@
         <v>131</v>
       </c>
       <c r="G38" t="n">
-        <v>140.5</v>
+        <v>138.3</v>
       </c>
       <c r="H38" t="n">
-        <v>151.5</v>
+        <v>148.5</v>
       </c>
       <c r="I38" t="n">
-        <v>201.3</v>
+        <v>197.8</v>
       </c>
       <c r="J38" t="n">
-        <v>217</v>
+        <v>211.8</v>
       </c>
       <c r="K38" t="n">
-        <v>278.1</v>
+        <v>272.8</v>
       </c>
       <c r="L38" t="n">
-        <v>373.6</v>
+        <v>288.4</v>
       </c>
     </row>
     <row r="39">
@@ -1886,22 +1912,22 @@
         <v>127.2</v>
       </c>
       <c r="G39" t="n">
-        <v>139</v>
+        <v>136.7</v>
       </c>
       <c r="H39" t="n">
-        <v>148.3</v>
+        <v>145.3</v>
       </c>
       <c r="I39" t="n">
-        <v>180.5</v>
+        <v>177.4</v>
       </c>
       <c r="J39" t="n">
-        <v>211</v>
+        <v>206.6</v>
       </c>
       <c r="K39" t="n">
-        <v>266.3</v>
+        <v>260.5</v>
       </c>
       <c r="L39" t="n">
-        <v>406.2</v>
+        <v>272</v>
       </c>
     </row>
     <row r="40">
@@ -1924,22 +1950,22 @@
         <v>115.9</v>
       </c>
       <c r="G40" t="n">
-        <v>128.7</v>
+        <v>127</v>
       </c>
       <c r="H40" t="n">
-        <v>137.3</v>
+        <v>135</v>
       </c>
       <c r="I40" t="n">
-        <v>158.6</v>
+        <v>155.7</v>
       </c>
       <c r="J40" t="n">
-        <v>194.6</v>
+        <v>191</v>
       </c>
       <c r="K40" t="n">
-        <v>246</v>
+        <v>241.5</v>
       </c>
       <c r="L40" t="n">
-        <v>379.3</v>
+        <v>267.4</v>
       </c>
     </row>
     <row r="41">
@@ -1962,21 +1988,23 @@
         <v>106</v>
       </c>
       <c r="G41" t="n">
-        <v>117.9</v>
+        <v>116.3</v>
       </c>
       <c r="H41" t="n">
-        <v>125.9</v>
+        <v>124</v>
       </c>
       <c r="I41" t="n">
-        <v>180.3</v>
+        <v>177.6</v>
       </c>
       <c r="J41" t="n">
-        <v>169.1</v>
+        <v>166.1</v>
       </c>
       <c r="K41" t="n">
-        <v>226.4</v>
-      </c>
-      <c r="L41" t="inlineStr"/>
+        <v>222.6</v>
+      </c>
+      <c r="L41" t="n">
+        <v>238</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1998,21 +2026,23 @@
         <v>83.7</v>
       </c>
       <c r="G42" t="n">
-        <v>98.5</v>
+        <v>97.8</v>
       </c>
       <c r="H42" t="n">
-        <v>101.7</v>
+        <v>100.9</v>
       </c>
       <c r="I42" t="n">
-        <v>136.9</v>
+        <v>135.6</v>
       </c>
       <c r="J42" t="n">
-        <v>141.1</v>
+        <v>139.6</v>
       </c>
       <c r="K42" t="n">
-        <v>203.4</v>
-      </c>
-      <c r="L42" t="inlineStr"/>
+        <v>201.5</v>
+      </c>
+      <c r="L42" t="n">
+        <v>194.9</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2034,21 +2064,23 @@
         <v>72.5</v>
       </c>
       <c r="G43" t="n">
-        <v>84.7</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>84.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>112.4</v>
+        <v>112.1</v>
       </c>
       <c r="J43" t="n">
-        <v>121.3</v>
+        <v>121.1</v>
       </c>
       <c r="K43" t="n">
-        <v>165.6</v>
-      </c>
-      <c r="L43" t="inlineStr"/>
+        <v>165.5</v>
+      </c>
+      <c r="L43" t="n">
+        <v>191.4</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2070,21 +2102,23 @@
         <v>68.90000000000001</v>
       </c>
       <c r="G44" t="n">
-        <v>73.90000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="H44" t="n">
-        <v>78.7</v>
+        <v>78.5</v>
       </c>
       <c r="I44" t="n">
-        <v>108.5</v>
+        <v>108.2</v>
       </c>
       <c r="J44" t="n">
-        <v>112.5</v>
+        <v>112.3</v>
       </c>
       <c r="K44" t="n">
-        <v>158.4</v>
-      </c>
-      <c r="L44" t="inlineStr"/>
+        <v>157.7</v>
+      </c>
+      <c r="L44" t="n">
+        <v>202.1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2109,16 +2143,16 @@
         <v>79.09999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>82.7</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>112.3</v>
+        <v>112.2</v>
       </c>
       <c r="J45" t="n">
-        <v>115.3</v>
+        <v>115.2</v>
       </c>
       <c r="K45" t="n">
-        <v>165.5</v>
+        <v>164.7</v>
       </c>
       <c r="L45" t="inlineStr"/>
     </row>
@@ -2144,19 +2178,19 @@
         <v>76.7</v>
       </c>
       <c r="G46" t="n">
-        <v>90.3</v>
+        <v>89.7</v>
       </c>
       <c r="H46" t="n">
-        <v>94.59999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="I46" t="n">
-        <v>126.2</v>
+        <v>125.2</v>
       </c>
       <c r="J46" t="n">
-        <v>135.2</v>
+        <v>134.1</v>
       </c>
       <c r="K46" t="n">
-        <v>181</v>
+        <v>179.5</v>
       </c>
       <c r="L46" t="inlineStr"/>
     </row>
@@ -2182,19 +2216,19 @@
         <v>102</v>
       </c>
       <c r="G47" t="n">
-        <v>119.8</v>
+        <v>117.4</v>
       </c>
       <c r="H47" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I47" t="n">
-        <v>155.1</v>
+        <v>152.3</v>
       </c>
       <c r="J47" t="n">
-        <v>178.9</v>
+        <v>176.1</v>
       </c>
       <c r="K47" t="n">
-        <v>240.8</v>
+        <v>236.8</v>
       </c>
       <c r="L47" t="inlineStr"/>
     </row>
@@ -2220,19 +2254,19 @@
         <v>116.6</v>
       </c>
       <c r="G48" t="n">
-        <v>137.4</v>
+        <v>134.5</v>
       </c>
       <c r="H48" t="n">
-        <v>152.5</v>
+        <v>149.3</v>
       </c>
       <c r="I48" t="n">
-        <v>195.5</v>
+        <v>191.7</v>
       </c>
       <c r="J48" t="n">
-        <v>205.8</v>
+        <v>202</v>
       </c>
       <c r="K48" t="n">
-        <v>275</v>
+        <v>269.9</v>
       </c>
       <c r="L48" t="inlineStr"/>
     </row>
@@ -2258,19 +2292,19 @@
         <v>129.9</v>
       </c>
       <c r="G49" t="n">
-        <v>159.8</v>
+        <v>156.5</v>
       </c>
       <c r="H49" t="n">
-        <v>188.9</v>
+        <v>185.3</v>
       </c>
       <c r="I49" t="n">
-        <v>207.5</v>
+        <v>203</v>
       </c>
       <c r="J49" t="n">
-        <v>264.1</v>
+        <v>259</v>
       </c>
       <c r="K49" t="n">
-        <v>306.3</v>
+        <v>299.9</v>
       </c>
       <c r="L49" t="inlineStr"/>
     </row>
